--- a/OPTO_INTEGRATIONS/BD_PROD.xlsx
+++ b/OPTO_INTEGRATIONS/BD_PROD.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://1masterlabotico-my.sharepoint.com/personal/gustavo_detoni_masterlabotico_com_br/Documents/Área de Trabalho/OPTO_SIOU_INTEGRATION/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://1masterlabotico-my.sharepoint.com/personal/gustavo_detoni_masterlabotico_com_br/Documents/Área de Trabalho/WMS/OPTO_INTEGRATIONS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="198" documentId="8_{F0901C24-956B-402B-BE01-7D9CFD9C380D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{845B3B3C-5C37-4210-8AA4-82135717D011}"/>
+  <xr:revisionPtr revIDLastSave="206" documentId="8_{F0901C24-956B-402B-BE01-7D9CFD9C380D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8B9AB89-9346-4348-8B15-F5A845DD9622}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9D6EA9-2669-44BE-BE71-C3511DC3591A}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8351" uniqueCount="2048">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8355" uniqueCount="2049">
   <si>
     <t>ACCESS CR39 SURF.</t>
   </si>
@@ -6164,6 +6164,9 @@
   </si>
   <si>
     <t>Nenhuma</t>
+  </si>
+  <si>
+    <t>MF EUROMIX PLUS 1.50 TRANSITIONS MARROM SURF.</t>
   </si>
 </sst>
 </file>
@@ -6235,8 +6238,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EFE6F96-0925-4CE0-824A-E207AB5AB3AF}" name="Tabela1" displayName="Tabela1" ref="A1:E2087" totalsRowShown="0" dataDxfId="3">
-  <autoFilter ref="A1:E2087" xr:uid="{9EFE6F96-0925-4CE0-824A-E207AB5AB3AF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EFE6F96-0925-4CE0-824A-E207AB5AB3AF}" name="Tabela1" displayName="Tabela1" ref="A1:E2088" totalsRowShown="0" dataDxfId="3">
+  <autoFilter ref="A1:E2088" xr:uid="{9EFE6F96-0925-4CE0-824A-E207AB5AB3AF}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{87F0DEFC-D8D5-4926-AEF8-99C389960A51}" name="COD" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{F310D51E-C86A-40E6-BF89-6BEEF2E596DE}" name="PRODUTO" dataDxfId="1"/>
@@ -6565,7 +6568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7386BA96-36F5-4DC1-9614-68BF693F53B0}">
-  <dimension ref="A1:E2087"/>
+  <dimension ref="A1:E2088"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
@@ -42053,6 +42056,23 @@
         <v>1655</v>
       </c>
     </row>
+    <row r="2088" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2088" s="1">
+        <v>7333</v>
+      </c>
+      <c r="B2088" s="1" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C2088" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D2088" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E2088" t="s">
+        <v>1655</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
   <tableParts count="1">

--- a/OPTO_INTEGRATIONS/BD_PROD.xlsx
+++ b/OPTO_INTEGRATIONS/BD_PROD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://1masterlabotico-my.sharepoint.com/personal/gustavo_detoni_masterlabotico_com_br/Documents/Área de Trabalho/WMS/OPTO_INTEGRATIONS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="283" documentId="8_{F0901C24-956B-402B-BE01-7D9CFD9C380D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82681E33-0316-4E24-84E7-8A9DB21F3206}"/>
+  <xr:revisionPtr revIDLastSave="386" documentId="8_{F0901C24-956B-402B-BE01-7D9CFD9C380D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F839D77D-5DC8-4BF3-8B78-C402215806A1}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9D6EA9-2669-44BE-BE71-C3511DC3591A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9D6EA9-2669-44BE-BE71-C3511DC3591A}"/>
   </bookViews>
   <sheets>
     <sheet name="todos os produtos" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10453" uniqueCount="2060">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11710" uniqueCount="2238">
   <si>
     <t>ACCESS CR39 SURF.</t>
   </si>
@@ -6196,20 +6196,561 @@
     <t>VS CR 1.49 INC (-200)</t>
   </si>
   <si>
-    <t>De papel</t>
-  </si>
-  <si>
     <t xml:space="preserve">VS ANTI REFLEXO 1.56 ACABADA </t>
+  </si>
+  <si>
+    <t>BF ULTEX CR 39 ACABADO</t>
+  </si>
+  <si>
+    <t>BF ULTEX CR39 ACABADA.</t>
+  </si>
+  <si>
+    <t>LENTE PARA OCULOS</t>
+  </si>
+  <si>
+    <t>LENTES MULTIFOCAIS</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 BLUE CUT AR AZUL +000-075/-075+075</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 BLUE CUT CIL ESTENDIDO RES AZUL</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 BLUE CUT CIL. ESTENDIDO AR AZUL</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 MC PHOTO BLUE CUT ESTENDIDO RES. AZUL</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 MCLEAN AR CIL. ESPECIAL -600/-400</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 MCLEAN AR CIL. ESTENDIDO -400/-200</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 MCLEAN AR ESPECIAL CIL -225/-400</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 MCLEAN AR ESPECIAL CIL -425/-600</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 MCLEAN AR ESPECIAL CIL -425/-6000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LP EUROPRO 1.56 MCLEAN AR PHOTO BLUE CUT ESPECIA RES. AZUL </t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 MCLEAN AR PHOTO BLUE CUT RES. AZUL</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 MCLEAN AR PHOTO BLUE CUT RES. VERDE</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 MCLEAN AR PHOTO CIL. ESTENDIDO</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 MCLEAN AR PHOTO ESPECIAL CIL -225/-400</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 MCLEAN BLUE CUT ESPECIAL RES VERDE CIL -425/-600</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.56 MCLEAN BLUE CUT ESPECIAL RES. AZUL -225/-400</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.59 POLY BLUE CUT CIL ESTENDIDO RES. AZUL</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.59 POLY BLUE CUT CIL ESTENDIDO RES. VERDE</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.59 POLY BLUE CUT ESPECIA RES. VERDE CIL -225/400</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.59 POLY BLUE CUT ESPECIAL RES. AZUL CIL -225/-400</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.59 POLY ESPECIAL MCLEAN AR CIL -2,25/-400</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.59 POLY MCLEAN AR ESPECIAL CIL -225/-400</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.59 POLY MCLEAN AR PHOTO CIL. ESTENDIDO</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.59 POLY MCLEAN AR PHOTO ESPECIAL CIL -225/-400</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.59 POLY PHOTO BC CIL. ESTENDIDO RES. AZUL</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.59 POLY PHOTO BLUE CUT ESPECIAL RES. AZUL -225/-400</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.60 BLUE CUT MCLEAN AR CIL. ESTENDIDO RES. VERDE</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.60 PHOTO ULTRAVEX BLUE CUT AR VERDE</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.67 MCLEAN AR BLUE CUT RES. AZUL CIL -225/-400</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.67 MCLEAN AR BLUE CUT RES. AZUL CIL -425/-600</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.67 MCLEAN AR BLUE CUT RES. VERDE CIL (-600)</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.67 MCLEAN AR BLUE CUT RES. VERDE CIL -225/-400</t>
+  </si>
+  <si>
+    <t>LP EUROPRO 1.74 MCLEAN AR ESF -12.00-10.50/CIL -2.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MF ACABADO 1.56 BLUE FILTER COM AR </t>
+  </si>
+  <si>
+    <t>MF ACABADO 1.56 INCOLOR C/AR.</t>
+  </si>
+  <si>
+    <t>MF ACABADO 1.56 PHOTO COM AR</t>
+  </si>
+  <si>
+    <t>VS 1.50  CRIZAL EASY</t>
+  </si>
+  <si>
+    <t>VS AIRWEAR 1.59 CRIZAL EASY PRO BLUE UV ACABADA.</t>
+  </si>
+  <si>
+    <t>VS AIRWEAR 1.59 CRIZAL ROCK BLUE UV ACABADA.</t>
+  </si>
+  <si>
+    <t>VS AIRWEAR 1.59 CRIZAL SAPPHIRE BLUEUV</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.56 ACABADA</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.56 ACABADA IN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VS ANTI REFLEXO 1.56 ESPECIAL ACABADA </t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.56 ESPECIAL OFTAL ACABADA</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.60 ULTRAVEX BLUE CUT RES. VERDE</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.60 ULTRAVEX ESPECIAL BLUE CUT RES. VERDE</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.60 ULTRAVEX PHOTO BLUE CUT RES. VERDE</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.61 ACABADA</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.61 ACABADA ESPECIAL</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.67 ACABADA</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.67 ESPECIAL ACABADA</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.67 ESPECIAL I ACABADA</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.67 FILTRO AZUL ESPECIAL</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.67 FILTRO ESPECIAL ACABADA</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.74 HIDROFOBICO</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.74 HIDROFOBICO -10 -300</t>
+  </si>
+  <si>
+    <t>VS ANTI REFLEXO 1.74 HIDROFOBICO ESF -12.00-10.50/CIL -2.00</t>
+  </si>
+  <si>
+    <t>VS ANTIREFLEXO 1.56</t>
+  </si>
+  <si>
+    <t>VS ANTIREFLEXO 1.60 BLUE CUT RES. VERDE</t>
+  </si>
+  <si>
+    <t>VS ANTIREFLEXO 1.67 BLUE CUT</t>
+  </si>
+  <si>
+    <t>VS ANTIREFLEXO 1.67 BLUE CUT ESPECIAL</t>
+  </si>
+  <si>
+    <t>VS ANTIREFLEXO 1.67 FILTRO AZUL</t>
+  </si>
+  <si>
+    <t>VS ANTIREFLEXO 1.74 FILTRO AZUL</t>
+  </si>
+  <si>
+    <t>VS BLOCO ESSILOR XPERIO 1.50 POLAR CINZA</t>
+  </si>
+  <si>
+    <t>VS BLUE CUT 1.56 ACABADA</t>
+  </si>
+  <si>
+    <t>VS BLUE CUT 1.56 ESPECIAL (-400) ACABADA</t>
+  </si>
+  <si>
+    <t>VS BLUE CUT 1.56 ESPECIAL (-600) ACABADA</t>
+  </si>
+  <si>
+    <t>VS CRIZAL PREVENCIA 1.50</t>
+  </si>
+  <si>
+    <t>VS CRIZAL ROCK UV 1.50</t>
+  </si>
+  <si>
+    <t>VS CRIZAL SAPPHIRE 1.50</t>
+  </si>
+  <si>
+    <t>VS ESSILOR EYEZEN BOOST 0,4 1.50 BLUE UV + AR CRIZAL EASY SURF.</t>
+  </si>
+  <si>
+    <t>VS FILTRO AZUL 1.56 (-400) ESPECIAL ACABADA</t>
+  </si>
+  <si>
+    <t>VS FILTRO AZUL 1.56 (-600) ESPECIAL ACABADA</t>
+  </si>
+  <si>
+    <t>VS FILTRO AZUL 1.56 ACABADA</t>
+  </si>
+  <si>
+    <t>VS HOYA BLUE CONTROL 1.50 ACABADA</t>
+  </si>
+  <si>
+    <t>VS HOYA HILUX 1.50 + LONGLIFE BLUECONTROL ACABADA.</t>
+  </si>
+  <si>
+    <t>VS HOYA HILUX 1.50 LONGLIFE UVCONTROL ACABADA.</t>
+  </si>
+  <si>
+    <t>VS HOYA HILUX 1.50 SENSITY 2 + LONGLIFE UVCONTROL ACABADA.</t>
+  </si>
+  <si>
+    <t>VS HOYA HILUX 1.50 SENSITY ORIGINAL + CLEAN EXTRA ACABADA.</t>
+  </si>
+  <si>
+    <t>VS HOYA HILUX 1.53 + LONGLIFE BLUE  CONTROL ACABADA.</t>
+  </si>
+  <si>
+    <t>VS HOYA HILUX 1.53 + LONGLIFE UVCONTROL ACABADA.</t>
+  </si>
+  <si>
+    <t>VS HOYA HILUX 1.53 SENSITY 2 + LONGLIFE UVCONTROL ACABADA.</t>
+  </si>
+  <si>
+    <t>VS HOYA MIYOSMART 1.59 INCOLOR</t>
+  </si>
+  <si>
+    <t>VS HOYA NULUX 1.60 + HIGH VISION MEIRYO ACABADA.</t>
+  </si>
+  <si>
+    <t>VS HOYA NULUX 1.60 + LONGLIFE UVCONTROL ACABADA.</t>
+  </si>
+  <si>
+    <t>VS HOYA NULUX 1.67 + HIGH VISION MEIRYO ACABADA.</t>
+  </si>
+  <si>
+    <t>VS HOYA NULUX 1.67 + LONGLIFE BLUE CONTROL ACABADA.</t>
+  </si>
+  <si>
+    <t>VS HOYA NULUX 1.67 + LONGLIFE UVCONTROL ACABADA.</t>
+  </si>
+  <si>
+    <t>VS HOYA NULUX 1.67 SENSITY 2 +  LONGLIFE UVCONTROL ACABADA.</t>
+  </si>
+  <si>
+    <t>VS KODAK 1.50 NO REFLEX</t>
+  </si>
+  <si>
+    <t>VS KODAK BLUE 1.56</t>
+  </si>
+  <si>
+    <t>VS KODAK CITY</t>
+  </si>
+  <si>
+    <t>VS KODAK CITY 1.59 POLY ACABADA.</t>
+  </si>
+  <si>
+    <t>VS KODAK INTRO 1.56</t>
+  </si>
+  <si>
+    <t>VS KODAK POLY BLUE ACABADA.</t>
+  </si>
+  <si>
+    <t>VS LONGLIFE 1.50 HOYA ACAB.</t>
+  </si>
+  <si>
+    <t>VS MIOLIGHT / HIPERLIGHT 1.67 BLUE CONTROL</t>
+  </si>
+  <si>
+    <t>VS MIOLIGHT 1.67 NO RISK ACABADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VS NPU TRUEFORM 1.50 NO RISK </t>
+  </si>
+  <si>
+    <t>VS PHOTO 1.67 AR ESPECIAL HIDROFÓBICO</t>
+  </si>
+  <si>
+    <t>VS PHOTO 1.67 AR HIDROFOBICO</t>
+  </si>
+  <si>
+    <t>VS PHOTO BLUE CUT 1.67 (-200) RES.AZUL</t>
+  </si>
+  <si>
+    <t>VS PHOTO BLUE CUT 1.67 (-400) RES.AZUL</t>
+  </si>
+  <si>
+    <t>VS PHOTO BLUE CUT 1.67 (ESF-10/-8,25) (CIL-300) RES.AZUL</t>
+  </si>
+  <si>
+    <t>VS PHOTOSSENSIVEL 1.56 ANTI REFLEXO ACABADA</t>
+  </si>
+  <si>
+    <t>VS PHOTOSSENSIVEL 1.56 ANTI REFLEXO ESPECIAL</t>
+  </si>
+  <si>
+    <t>VS PHOTOSSENSIVEL 1.56 BLUE CUT ESPECIAL (RES. AZUL)</t>
+  </si>
+  <si>
+    <t>VS PHOTOSSENSIVEL BLUE CUT 1.56 (RES . AZUL)</t>
+  </si>
+  <si>
+    <t>VS PHOTOSSENSIVEL BLUE CUT 1.56 AR (RES . AZUL)</t>
+  </si>
+  <si>
+    <t>VS PHOTOSSENSIVEL FILTRO AZUL 1.56 ANTI REFLEXO</t>
+  </si>
+  <si>
+    <t>VS PHOTOSSENSIVEL FILTRO AZUL 1.56 ESPECIAL ANTI REFLEXO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VS POLICARBONATO 1.59 BLUE CUT </t>
+  </si>
+  <si>
+    <t>VS POLICARBONATO 1.59 PHOTO BLUE CUT</t>
+  </si>
+  <si>
+    <t>VS POLICARBONATO 1.59 PHOTO BLUE CUT ESPECIAL</t>
+  </si>
+  <si>
+    <t>VS POLICARBONATO ANTI REFLEXO 1.59 ACABADA</t>
+  </si>
+  <si>
+    <t>VS POLICARBONATO ANTI REFLEXO 1.59 ESPECIAL ACABADA</t>
+  </si>
+  <si>
+    <t>VS POLICARBONATO BLUE CUT 1.59 ESPECIAL</t>
+  </si>
+  <si>
+    <t>VS POLICARBONATO FILTRO AZUL 1.59</t>
+  </si>
+  <si>
+    <t>VS POLICARBONATO FILTRO AZUL 1.59 ESPECIAL</t>
+  </si>
+  <si>
+    <t>VS POLICARBONATO INCOLOR 1.59 ACABADA</t>
+  </si>
+  <si>
+    <t>VS POLICARBONATO INCOLOR ESPECIAL 1.59 ACABADA</t>
+  </si>
+  <si>
+    <t>VS POLICARBONATO PHOTO 1.59 ANTIREFLEXO</t>
+  </si>
+  <si>
+    <t>VS POLICARBONATO PHOTO 1.59 ESPECIAL</t>
+  </si>
+  <si>
+    <t>VS SOLAR CR-39 INCOLOR</t>
+  </si>
+  <si>
+    <t>VS SOLAR DEGRADE CR-39 CURVA 6 CINZA</t>
+  </si>
+  <si>
+    <t>VS SOLAR DEGRADE CR-39 CURVA 6 G-15</t>
+  </si>
+  <si>
+    <t>VS SOLAR DEGRADE CR-39 CURVA 6 MARROM</t>
+  </si>
+  <si>
+    <t>VS SOLAR DEGRADE CR-39 CURVA 8 CINZA</t>
+  </si>
+  <si>
+    <t>VS SOLAR DEGRADE CR-39 CURVA 8 G-15</t>
+  </si>
+  <si>
+    <t>VS SOLAR DEGRADE CR-39 CURVA 8 MARROM</t>
+  </si>
+  <si>
+    <t>VS SOLAR ESPELHADO CR 39 (PRATA/AZUL/LARANJA/DOURADA/VERDE)</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLARIZADA AZUL DEGRADE LAMINA</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLARIZADA C4  MARROM DEGRADE LAMIN</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLARIZADA CINZA C4  DEGRADE LAMINA</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLARIZADA CINZA LAMINA C4</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLARIZADA CINZA LAMINA C6</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLARIZADA ESPELHADA</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLARIZADA G-15 DEGRADE LAMINA</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLARIZADA G-15 LAMINA</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLARIZADA MARROM C6 DEGRADE LAMIN</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLARIZADA MARROM LAMINA</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLARIZADA NIGHT DRIVE C4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VS SOLAR POLICARBONATO CURVA 6 CINZA </t>
+  </si>
+  <si>
+    <t>VS SOLAR POLICARBONATO CURVA 6 CINZA DEGRADE</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLICARBONATO CURVA 6 ESPELHADA PRATA</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLICARBONATO CURVA 6 G-15</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLICARBONATO CURVA 6 MARROM</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLICARBONATO CURVA 6 MARROM DEGRADE</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLICARBONATO CURVA 8 CINZA</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLICARBONATO CURVA 8 CINZA DEGRADE</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLICARBONATO CURVA 8 G-15</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLICARBONATO CURVA 8 MARROM</t>
+  </si>
+  <si>
+    <t>VS SOLAR POLICARBONATO CURVA 8 MARROM DEGRADE</t>
+  </si>
+  <si>
+    <t>VS SOLAR TOTAL CR-39 CURVA 6 BLACK</t>
+  </si>
+  <si>
+    <t>VS SOLAR TOTAL CR-39 CURVA 6 CINZA</t>
+  </si>
+  <si>
+    <t>VS SOLAR TOTAL CR-39 CURVA 6 FASCHION</t>
+  </si>
+  <si>
+    <t>VS SOLAR TOTAL CR-39 CURVA 6 G-15</t>
+  </si>
+  <si>
+    <t>VS SOLAR TOTAL CR-39 CURVA 6 MARROM</t>
+  </si>
+  <si>
+    <t>VS SOLAR TOTAL CR-39 CURVA 8 BLACK</t>
+  </si>
+  <si>
+    <t>VS SOLAR TOTAL CR-39 CURVA 8 CINZA</t>
+  </si>
+  <si>
+    <t>VS SOLAR TOTAL CR-39 CURVA 8 FASCHION</t>
+  </si>
+  <si>
+    <t>VS SOLAR TOTAL CR-39 CURVA 8 G-15</t>
+  </si>
+  <si>
+    <t>VS SOLAR TOTAL CR-39 CURVA 8 MARROM</t>
+  </si>
+  <si>
+    <t>VS STYLIS 1.67 CRIZAL SAPPHIRE HR BLUE UV ACABADA.</t>
+  </si>
+  <si>
+    <t>VS SYNC 9 NORISK + BLUE CONTROL 1.50</t>
+  </si>
+  <si>
+    <t>VS TRANSITIONS CINZA CRIZAL EASY 1.50 ACABADA</t>
+  </si>
+  <si>
+    <t>VS TRANSITIONS CRIZAL SAPPHIRE 1.50 ACABADA</t>
+  </si>
+  <si>
+    <t>VS TRANSITIONS GEN8 ACABADA</t>
+  </si>
+  <si>
+    <t>VS TRANSITIONS MARROM ACABADA</t>
+  </si>
+  <si>
+    <t>VS TRANSITIONS SIGNATURE VII ACABADA.</t>
+  </si>
+  <si>
+    <t>VS TRIO EASY CLEAN 1.50 ACABADA</t>
+  </si>
+  <si>
+    <t>VS TRUE FORM 1.67</t>
+  </si>
+  <si>
+    <t>VS ULTRASFERIC 1.60</t>
+  </si>
+  <si>
+    <t>VS ULTRAX POLICARBONATO 1.59 AR AQUA</t>
+  </si>
+  <si>
+    <t>Papel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -6235,12 +6776,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6275,8 +6820,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EFE6F96-0925-4CE0-824A-E207AB5AB3AF}" name="Tabela1" displayName="Tabela1" ref="A1:F2090" totalsRowShown="0" dataDxfId="4">
-  <autoFilter ref="A1:F2090" xr:uid="{9EFE6F96-0925-4CE0-824A-E207AB5AB3AF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EFE6F96-0925-4CE0-824A-E207AB5AB3AF}" name="Tabela1" displayName="Tabela1" ref="A1:F2341" totalsRowShown="0" dataDxfId="4">
+  <autoFilter ref="A1:F2341" xr:uid="{9EFE6F96-0925-4CE0-824A-E207AB5AB3AF}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A185:F2341">
+    <sortCondition ref="E1:E2341"/>
+  </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{87F0DEFC-D8D5-4926-AEF8-99C389960A51}" name="COD" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{F310D51E-C86A-40E6-BF89-6BEEF2E596DE}" name="PRODUTO" dataDxfId="2"/>
@@ -6606,11 +7154,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7386BA96-36F5-4DC1-9614-68BF693F53B0}">
-  <dimension ref="A1:F2090"/>
+  <dimension ref="A1:F2341"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
-    <col min="2" max="2" width="68.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="77.42578125" customWidth="1"/>
     <col min="3" max="3" width="47.85546875" customWidth="1"/>
     <col min="4" max="7" width="60.28515625" customWidth="1"/>
   </cols>
@@ -10297,402 +10845,402 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
-        <v>10772</v>
+        <v>1004</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C185" t="s">
         <v>2049</v>
       </c>
       <c r="D185" t="s">
-        <v>1652</v>
+        <v>2047</v>
       </c>
       <c r="E185" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>2056</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
-        <v>10751</v>
+        <v>1005</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C186" t="s">
         <v>2049</v>
       </c>
       <c r="D186" t="s">
-        <v>1652</v>
+        <v>2047</v>
       </c>
       <c r="E186" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>2056</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" s="1">
-        <v>1075</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C187" t="s">
+      <c r="A187" s="2">
+        <v>1114</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D187" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E187" t="s">
-        <v>1656</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>2056</v>
+      <c r="D187" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" s="1">
-        <v>1079</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C188" t="s">
+      <c r="A188" s="2">
+        <v>1166</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>2059</v>
+      </c>
+      <c r="C188" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D188" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E188" t="s">
-        <v>1656</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>2056</v>
+      <c r="D188" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189" s="1">
-        <v>10771</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C189" t="s">
+      <c r="A189" s="2">
+        <v>1202</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>2060</v>
+      </c>
+      <c r="C189" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D189" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E189" t="s">
-        <v>1656</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>2056</v>
+      <c r="D189" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190" s="1">
-        <v>1077</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C190" t="s">
+      <c r="A190" s="2">
+        <v>900</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C190" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D190" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E190" t="s">
-        <v>1656</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>2056</v>
+      <c r="D190" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A191" s="1">
-        <v>1078</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C191" t="s">
+      <c r="A191" s="2">
+        <v>99992</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C191" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D191" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E191" t="s">
-        <v>1656</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>2056</v>
+      <c r="D191" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192" s="1">
-        <v>10752</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C192" t="s">
+      <c r="A192" s="2">
+        <v>1004</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C192" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D192" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E192" t="s">
-        <v>1656</v>
-      </c>
-      <c r="F192" s="1" t="s">
-        <v>2056</v>
+      <c r="D192" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A193" s="1">
-        <v>1076</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C193" t="s">
+      <c r="A193" s="2">
+        <v>1005</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C193" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D193" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E193" t="s">
-        <v>1656</v>
-      </c>
-      <c r="F193" s="1" t="s">
-        <v>2056</v>
+      <c r="D193" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A194" s="1">
-        <v>10891</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C194" t="s">
+      <c r="A194" s="2">
+        <v>1181</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>2099</v>
+      </c>
+      <c r="C194" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D194" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E194" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F194" s="1" t="s">
-        <v>2056</v>
+      <c r="D194" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A195" s="1">
-        <v>1089</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C195" t="s">
+      <c r="A195" s="2">
+        <v>2259</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C195" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D195" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E195" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>2056</v>
+      <c r="D195" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A196" s="1">
-        <v>10892</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C196" t="s">
+      <c r="A196" s="2">
+        <v>1189</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C196" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D196" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E196" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F196" s="1" t="s">
-        <v>2056</v>
+      <c r="D196" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A197" s="1">
-        <v>1090</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C197" t="s">
+      <c r="A197" s="2">
+        <v>1194</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C197" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D197" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E197" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F197" s="1" t="s">
-        <v>2056</v>
+      <c r="D197" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A198" s="1">
-        <v>10912</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C198" t="s">
+      <c r="A198" s="2">
+        <v>5616</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C198" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D198" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E198" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F198" s="1" t="s">
-        <v>2056</v>
+      <c r="D198" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A199" s="1">
-        <v>1092</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C199" t="s">
+      <c r="A199" s="2">
+        <v>5877</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C199" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D199" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E199" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F199" s="1" t="s">
-        <v>2056</v>
+      <c r="D199" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" s="1">
-        <v>10911</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C200" t="s">
+      <c r="A200" s="2">
+        <v>1167</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C200" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D200" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E200" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F200" s="1" t="s">
-        <v>2056</v>
+      <c r="D200" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" s="1">
-        <v>1091</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C201" t="s">
+      <c r="A201" s="2">
+        <v>5868</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C201" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D201" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E201" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F201" s="1" t="s">
-        <v>2056</v>
+      <c r="D201" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" s="1">
-        <v>10941</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C202" t="s">
+      <c r="A202" s="2">
+        <v>5867</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C202" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D202" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E202" t="s">
-        <v>1657</v>
-      </c>
-      <c r="F202" s="1" t="s">
-        <v>2056</v>
+      <c r="D202" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" s="1">
-        <v>11841</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C203" t="s">
+      <c r="A203" s="2">
+        <v>5908</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C203" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D203" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E203" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F203" s="1" t="s">
-        <v>2056</v>
+      <c r="D203" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204" s="1">
-        <v>11842</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C204" t="s">
+      <c r="A204" s="2">
+        <v>5866</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D204" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E204" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F204" s="1" t="s">
-        <v>2056</v>
+      <c r="D204" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -20276,1223 +20824,1223 @@
       </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A684" s="1">
-        <v>1004</v>
-      </c>
-      <c r="B684" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C684" t="s">
+      <c r="A684" s="2">
+        <v>5864</v>
+      </c>
+      <c r="B684" s="2" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C684" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D684" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E684" t="s">
-        <v>1655</v>
-      </c>
-      <c r="F684" s="1" t="s">
-        <v>2056</v>
+      <c r="D684" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E684" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F684" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A685" s="1">
-        <v>1005</v>
-      </c>
-      <c r="B685" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C685" t="s">
+      <c r="A685" s="2">
+        <v>5865</v>
+      </c>
+      <c r="B685" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C685" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D685" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E685" t="s">
-        <v>1655</v>
-      </c>
-      <c r="F685" s="1" t="s">
-        <v>2056</v>
+      <c r="D685" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E685" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F685" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A686" s="1">
+      <c r="A686" s="2">
+        <v>5869</v>
+      </c>
+      <c r="B686" s="2" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C686" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D686" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E686" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F686" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A687" s="2">
+        <v>5875</v>
+      </c>
+      <c r="B687" s="2" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C687" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D687" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E687" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F687" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="688" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A688" s="2">
+        <v>1195</v>
+      </c>
+      <c r="B688" s="2" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C688" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D688" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E688" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F688" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="689" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A689" s="2">
+        <v>5919</v>
+      </c>
+      <c r="B689" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C689" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D689" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E689" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F689" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A690" s="2">
+        <v>1203</v>
+      </c>
+      <c r="B690" s="2" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C690" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D690" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E690" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F690" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="691" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A691" s="2">
+        <v>1178</v>
+      </c>
+      <c r="B691" s="2" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C691" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D691" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E691" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F691" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A692" s="2">
+        <v>1177</v>
+      </c>
+      <c r="B692" s="2" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C692" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D692" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E692" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F692" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A693" s="2">
+        <v>1179</v>
+      </c>
+      <c r="B693" s="2" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C693" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D693" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E693" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F693" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A694" s="2">
+        <v>1172</v>
+      </c>
+      <c r="B694" s="2" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C694" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D694" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E694" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F694" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A695" s="2">
+        <v>1126</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C695" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D695" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E695" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F695" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A696" s="2">
+        <v>1125</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C696" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D696" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E696" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F696" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A697" s="2">
+        <v>1198</v>
+      </c>
+      <c r="B697" s="2" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C697" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D697" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E697" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F697" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A698" s="2">
+        <v>10772</v>
+      </c>
+      <c r="B698" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C698" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D698" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E698" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F698" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A699" s="2">
+        <v>10751</v>
+      </c>
+      <c r="B699" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C699" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D699" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E699" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F699" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A700" s="2">
+        <v>1075</v>
+      </c>
+      <c r="B700" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C700" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D700" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E700" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F700" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="701" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A701" s="2">
+        <v>1079</v>
+      </c>
+      <c r="B701" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C701" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D701" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E701" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F701" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="702" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A702" s="2">
+        <v>10771</v>
+      </c>
+      <c r="B702" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C702" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D702" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E702" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F702" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="703" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A703" s="2">
+        <v>1077</v>
+      </c>
+      <c r="B703" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C703" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D703" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E703" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F703" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="704" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A704" s="2">
+        <v>1078</v>
+      </c>
+      <c r="B704" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C704" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D704" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E704" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F704" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="705" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A705" s="2">
+        <v>10752</v>
+      </c>
+      <c r="B705" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C705" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D705" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E705" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F705" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="706" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A706" s="2">
+        <v>1076</v>
+      </c>
+      <c r="B706" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C706" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D706" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E706" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F706" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="707" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A707" s="2">
         <v>11711</v>
       </c>
-      <c r="B686" s="1" t="s">
+      <c r="B707" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C686" t="s">
+      <c r="C707" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D686" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E686" t="s">
+      <c r="D707" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E707" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F686" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A687" s="1" t="s">
+      <c r="F707" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="708" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A708" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B687" s="1" t="s">
+      <c r="B708" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C687" t="s">
+      <c r="C708" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D687" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E687" t="s">
+      <c r="D708" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E708" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F687" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="688" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A688" s="1">
+      <c r="F708" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="709" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A709" s="2">
         <v>11713</v>
       </c>
-      <c r="B688" s="1" t="s">
+      <c r="B709" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C688" t="s">
+      <c r="C709" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D688" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E688" t="s">
+      <c r="D709" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E709" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F688" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="689" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A689" s="1">
+      <c r="F709" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="710" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A710" s="2">
         <v>10132</v>
       </c>
-      <c r="B689" s="1" t="s">
+      <c r="B710" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C689" t="s">
+      <c r="C710" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D689" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E689" t="s">
+      <c r="D710" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E710" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F689" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A690" s="1">
+      <c r="F710" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="711" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A711" s="2">
         <v>11712</v>
       </c>
-      <c r="B690" s="1" t="s">
+      <c r="B711" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C690" t="s">
+      <c r="C711" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D690" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E690" t="s">
+      <c r="D711" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E711" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F690" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="691" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A691" s="1">
+      <c r="F711" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="712" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A712" s="2">
         <v>10133</v>
       </c>
-      <c r="B691" s="1" t="s">
+      <c r="B712" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C691" t="s">
+      <c r="C712" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D691" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E691" t="s">
+      <c r="D712" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E712" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F691" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A692" s="1">
+      <c r="F712" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="713" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A713" s="2">
         <v>1019</v>
       </c>
-      <c r="B692" s="1" t="s">
+      <c r="B713" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C692" t="s">
+      <c r="C713" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D692" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E692" t="s">
+      <c r="D713" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E713" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F692" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A693" s="1">
+      <c r="F713" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="714" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A714" s="2">
         <v>1014</v>
       </c>
-      <c r="B693" s="1" t="s">
+      <c r="B714" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C693" t="s">
+      <c r="C714" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D693" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E693" t="s">
+      <c r="D714" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E714" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F693" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A694" s="1">
+      <c r="F714" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="715" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A715" s="2">
         <v>10163</v>
       </c>
-      <c r="B694" s="1" t="s">
+      <c r="B715" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C694" t="s">
+      <c r="C715" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D694" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E694" t="s">
+      <c r="D715" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E715" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F694" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A695" s="1">
+      <c r="F715" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="716" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A716" s="2">
         <v>10162</v>
       </c>
-      <c r="B695" s="1" t="s">
+      <c r="B716" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C695" t="s">
+      <c r="C716" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D695" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E695" t="s">
+      <c r="D716" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E716" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F695" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A696" s="1">
+      <c r="F716" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="717" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A717" s="2">
         <v>1016</v>
       </c>
-      <c r="B696" s="1" t="s">
+      <c r="B717" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C696" t="s">
+      <c r="C717" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D696" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E696" t="s">
+      <c r="D717" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E717" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F696" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A697" s="1">
+      <c r="F717" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="718" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A718" s="2">
         <v>1013</v>
       </c>
-      <c r="B697" s="1" t="s">
+      <c r="B718" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C697" t="s">
+      <c r="C718" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D697" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E697" t="s">
+      <c r="D718" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E718" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F697" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A698" s="1">
+      <c r="F718" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="719" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A719" s="2">
         <v>10161</v>
       </c>
-      <c r="B698" s="1" t="s">
+      <c r="B719" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C698" t="s">
+      <c r="C719" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D698" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E698" t="s">
+      <c r="D719" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E719" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F698" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A699" s="1">
+      <c r="F719" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="720" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A720" s="2">
         <v>10091</v>
       </c>
-      <c r="B699" s="1" t="s">
+      <c r="B720" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C699" t="s">
+      <c r="C720" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D699" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E699" t="s">
+      <c r="D720" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E720" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F699" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A700" s="1" t="s">
+      <c r="F720" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="721" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A721" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B700" s="1" t="s">
+      <c r="B721" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C700" t="s">
+      <c r="C721" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D700" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E700" t="s">
+      <c r="D721" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E721" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F700" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="701" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A701" s="1">
+      <c r="F721" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="722" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A722" s="2">
         <v>10093</v>
       </c>
-      <c r="B701" s="1" t="s">
+      <c r="B722" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C701" t="s">
+      <c r="C722" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D701" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E701" t="s">
+      <c r="D722" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E722" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F701" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="702" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A702" s="1">
+      <c r="F722" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="723" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A723" s="2">
         <v>10092</v>
       </c>
-      <c r="B702" s="1" t="s">
+      <c r="B723" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C702" t="s">
+      <c r="C723" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D702" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E702" t="s">
+      <c r="D723" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E723" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F702" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="703" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A703" s="1">
+      <c r="F723" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="724" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A724" s="2">
         <v>1011</v>
       </c>
-      <c r="B703" s="1" t="s">
+      <c r="B724" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C703" t="s">
+      <c r="C724" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D703" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E703" t="s">
+      <c r="D724" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E724" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F703" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="704" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A704" s="1">
+      <c r="F724" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="725" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A725" s="2">
         <v>1012</v>
       </c>
-      <c r="B704" s="1" t="s">
+      <c r="B725" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C704" t="s">
+      <c r="C725" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D704" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E704" t="s">
+      <c r="D725" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E725" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F704" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="705" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A705" s="1">
+      <c r="F725" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="726" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A726" s="2">
         <v>10094</v>
       </c>
-      <c r="B705" s="1" t="s">
+      <c r="B726" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C705" t="s">
+      <c r="C726" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D705" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E705" t="s">
+      <c r="D726" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E726" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F705" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="706" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A706" s="1">
+      <c r="F726" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="727" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A727" s="2">
         <v>1010</v>
       </c>
-      <c r="B706" s="1" t="s">
+      <c r="B727" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C706" t="s">
+      <c r="C727" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D706" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E706" t="s">
+      <c r="D727" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E727" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F706" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="707" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A707" s="1">
+      <c r="F727" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="728" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A728" s="2">
         <v>1017</v>
       </c>
-      <c r="B707" s="1" t="s">
+      <c r="B728" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C707" t="s">
+      <c r="C728" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D707" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E707" t="s">
+      <c r="D728" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E728" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F707" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="708" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A708" s="1">
+      <c r="F728" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="729" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A729" s="2">
         <v>1015</v>
       </c>
-      <c r="B708" s="1" t="s">
+      <c r="B729" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C708" t="s">
+      <c r="C729" s="3" t="s">
         <v>2049</v>
       </c>
-      <c r="D708" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E708" t="s">
+      <c r="D729" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E729" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F708" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="709" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A709" s="1">
-        <v>10802</v>
-      </c>
-      <c r="B709" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C709" t="s">
+      <c r="F729" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="730" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A730" s="2">
+        <v>1009</v>
+      </c>
+      <c r="B730" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C730" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D709" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E709" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F709" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="710" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A710" s="1">
-        <v>10822</v>
-      </c>
-      <c r="B710" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C710" t="s">
+      <c r="D730" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E730" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F730" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="731" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A731" s="2">
+        <v>1102</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C731" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D710" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E710" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F710" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="711" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A711" s="1">
-        <v>1083</v>
-      </c>
-      <c r="B711" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C711" t="s">
+      <c r="D731" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E731" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F731" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="732" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A732" s="2">
+        <v>11711</v>
+      </c>
+      <c r="B732" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C732" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D711" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E711" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F711" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="712" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A712" s="1">
-        <v>1081</v>
-      </c>
-      <c r="B712" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C712" t="s">
+      <c r="D732" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E732" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F732" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="733" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A733" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C733" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D712" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E712" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F712" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="713" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A713" s="1">
-        <v>10821</v>
-      </c>
-      <c r="B713" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C713" t="s">
+      <c r="D733" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E733" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F733" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="734" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A734" s="2">
+        <v>11713</v>
+      </c>
+      <c r="B734" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C734" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D713" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E713" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F713" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="714" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A714" s="1">
-        <v>10801</v>
-      </c>
-      <c r="B714" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C714" t="s">
+      <c r="D734" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E734" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F734" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="735" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A735" s="2">
+        <v>10132</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>2064</v>
+      </c>
+      <c r="C735" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D714" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E714" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F714" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="715" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A715" s="1">
-        <v>1080</v>
-      </c>
-      <c r="B715" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C715" t="s">
+      <c r="D735" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E735" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F735" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="736" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A736" s="2">
+        <v>11712</v>
+      </c>
+      <c r="B736" s="2" t="s">
+        <v>2065</v>
+      </c>
+      <c r="C736" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D715" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E715" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F715" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="716" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A716" s="1">
-        <v>1084</v>
-      </c>
-      <c r="B716" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C716" t="s">
+      <c r="D736" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E736" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F736" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="737" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A737" s="2">
+        <v>1014</v>
+      </c>
+      <c r="B737" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C737" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D716" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E716" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F716" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="717" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A717" s="1">
-        <v>1086</v>
-      </c>
-      <c r="B717" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C717" t="s">
+      <c r="D737" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E737" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F737" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="738" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A738" s="2">
+        <v>1019</v>
+      </c>
+      <c r="B738" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C738" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D717" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E717" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F717" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="718" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A718" s="1">
-        <v>10851</v>
-      </c>
-      <c r="B718" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C718" t="s">
+      <c r="D738" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E738" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F738" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="739" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A739" s="2">
+        <v>10133</v>
+      </c>
+      <c r="B739" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C739" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D718" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E718" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F718" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="719" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A719" s="1">
-        <v>1085</v>
-      </c>
-      <c r="B719" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C719" t="s">
+      <c r="D739" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E739" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F739" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="740" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A740" s="2">
+        <v>10163</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C740" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D719" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E719" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F719" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="720" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A720" s="1">
-        <v>10852</v>
-      </c>
-      <c r="B720" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C720" t="s">
+      <c r="D740" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E740" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F740" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="741" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A741" s="2">
+        <v>10162</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C741" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D720" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E720" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F720" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="721" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A721" s="1">
-        <v>10871</v>
-      </c>
-      <c r="B721" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C721" t="s">
+      <c r="D741" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E741" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F741" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="742" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A742" s="2">
+        <v>1016</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C742" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D721" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E721" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F721" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="722" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A722" s="1">
-        <v>1087</v>
-      </c>
-      <c r="B722" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C722" t="s">
+      <c r="D742" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E742" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F742" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="743" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A743" s="2">
+        <v>1013</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C743" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D722" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E722" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F722" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="723" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A723" s="1">
-        <v>10872</v>
-      </c>
-      <c r="B723" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C723" t="s">
+      <c r="D743" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E743" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F743" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="744" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A744" s="2">
+        <v>10161</v>
+      </c>
+      <c r="B744" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C744" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D723" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E723" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F723" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="724" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A724" s="1">
-        <v>1088</v>
-      </c>
-      <c r="B724" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C724" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D724" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E724" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F724" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="725" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A725" s="1">
-        <v>10952</v>
-      </c>
-      <c r="B725" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C725" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D725" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E725" t="s">
-        <v>1657</v>
-      </c>
-      <c r="F725" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="726" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A726" s="1">
-        <v>10951</v>
-      </c>
-      <c r="B726" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C726" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D726" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E726" t="s">
-        <v>1657</v>
-      </c>
-      <c r="F726" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="727" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A727" s="1">
-        <v>1095</v>
-      </c>
-      <c r="B727" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C727" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D727" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E727" t="s">
-        <v>1657</v>
-      </c>
-      <c r="F727" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="728" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A728" s="1">
-        <v>10931</v>
-      </c>
-      <c r="B728" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C728" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D728" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E728" t="s">
-        <v>1657</v>
-      </c>
-      <c r="F728" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="729" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A729" s="1">
-        <v>1093</v>
-      </c>
-      <c r="B729" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C729" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D729" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E729" t="s">
-        <v>1657</v>
-      </c>
-      <c r="F729" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="730" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A730" s="1">
-        <v>10932</v>
-      </c>
-      <c r="B730" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C730" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D730" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E730" t="s">
-        <v>1657</v>
-      </c>
-      <c r="F730" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="731" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A731" s="1">
-        <v>10961</v>
-      </c>
-      <c r="B731" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C731" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D731" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E731" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F731" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="732" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A732" s="1">
-        <v>10971</v>
-      </c>
-      <c r="B732" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C732" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D732" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E732" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F732" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="733" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A733" s="1">
-        <v>10972</v>
-      </c>
-      <c r="B733" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C733" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D733" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E733" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F733" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="734" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A734" s="1">
-        <v>10973</v>
-      </c>
-      <c r="B734" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C734" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D734" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E734" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F734" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="735" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A735" s="1">
-        <v>10981</v>
-      </c>
-      <c r="B735" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C735" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D735" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E735" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F735" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="736" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A736" s="1">
-        <v>1098</v>
-      </c>
-      <c r="B736" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C736" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D736" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E736" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F736" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="737" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A737" s="1">
-        <v>10983</v>
-      </c>
-      <c r="B737" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C737" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D737" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E737" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F737" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="738" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A738" s="1">
-        <v>10982</v>
-      </c>
-      <c r="B738" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C738" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D738" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E738" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F738" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="739" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A739" s="1">
-        <v>10962</v>
-      </c>
-      <c r="B739" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C739" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D739" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E739" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F739" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="740" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A740" s="1">
-        <v>10963</v>
-      </c>
-      <c r="B740" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C740" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D740" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E740" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F740" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="741" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A741" s="1">
-        <v>11011</v>
-      </c>
-      <c r="B741" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C741" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D741" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E741" t="s">
-        <v>1661</v>
-      </c>
-      <c r="F741" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="742" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A742" s="1">
-        <v>11003</v>
-      </c>
-      <c r="B742" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C742" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D742" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E742" t="s">
-        <v>1661</v>
-      </c>
-      <c r="F742" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="743" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A743" s="1">
-        <v>11002</v>
-      </c>
-      <c r="B743" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C743" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D743" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E743" t="s">
-        <v>1661</v>
-      </c>
-      <c r="F743" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="744" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A744" s="1">
-        <v>11001</v>
-      </c>
-      <c r="B744" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C744" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D744" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E744" t="s">
-        <v>1661</v>
-      </c>
-      <c r="F744" s="1" t="s">
-        <v>2056</v>
+      <c r="D744" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E744" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F744" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="745" spans="1:6" x14ac:dyDescent="0.25">
@@ -41776,83 +42324,83 @@
       </c>
     </row>
     <row r="1759" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1759" s="1">
+      <c r="A1759" s="2">
+        <v>10772</v>
+      </c>
+      <c r="B1759" s="2" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C1759" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D1759" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E1759" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F1759" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1760" s="2">
+        <v>10091</v>
+      </c>
+      <c r="B1760" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1760" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D1760" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E1760" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F1760" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1761" s="2">
         <v>1009</v>
       </c>
-      <c r="B1759" s="1" t="s">
+      <c r="B1761" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C1759" s="1" t="s">
+      <c r="C1761" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D1759" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E1759" t="s">
+      <c r="D1761" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E1761" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F1759" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="1760" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1760" s="1">
-        <v>1082</v>
-      </c>
-      <c r="B1760" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1760" s="1" t="s">
+      <c r="F1761" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1762" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1762" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1762" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D1760" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E1760" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F1760" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="1761" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1761" s="1">
-        <v>11691</v>
-      </c>
-      <c r="B1761" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C1761" s="1" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D1761" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E1761" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F1761" s="1" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="1762" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1762" s="1">
-        <v>11692</v>
-      </c>
-      <c r="B1762" s="1" t="s">
-        <v>1725</v>
-      </c>
-      <c r="C1762" s="1" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D1762" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E1762" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F1762" s="1" t="s">
-        <v>2056</v>
+      <c r="D1762" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E1762" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F1762" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="1763" spans="1:6" x14ac:dyDescent="0.25">
@@ -48376,49 +48924,5070 @@
       </c>
     </row>
     <row r="2089" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2089" s="1">
-        <v>1114</v>
-      </c>
-      <c r="B2089" s="1" t="s">
+      <c r="A2089" s="2">
+        <v>10093</v>
+      </c>
+      <c r="B2089" s="2" t="s">
+        <v>2067</v>
+      </c>
+      <c r="C2089" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2089" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2089" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2089" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2090" s="2">
+        <v>10092</v>
+      </c>
+      <c r="B2090" s="2" t="s">
+        <v>2068</v>
+      </c>
+      <c r="C2090" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2090" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2090" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2090" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2091" s="2">
+        <v>1011</v>
+      </c>
+      <c r="B2091" s="2" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C2091" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2091" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2091" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2091" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2092" s="2">
+        <v>1012</v>
+      </c>
+      <c r="B2092" s="2" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C2092" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2092" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2092" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2092" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2093" s="2">
+        <v>10094</v>
+      </c>
+      <c r="B2093" s="2" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2093" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2093" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2093" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2093" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2094" s="2">
+        <v>1075</v>
+      </c>
+      <c r="B2094" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2094" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2094" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2094" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2094" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2095" s="2">
+        <v>10751</v>
+      </c>
+      <c r="B2095" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2095" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2095" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2095" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2095" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2096" s="2">
+        <v>1079</v>
+      </c>
+      <c r="B2096" s="2" t="s">
+        <v>2072</v>
+      </c>
+      <c r="C2096" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2096" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2096" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2096" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2097" s="2">
+        <v>1077</v>
+      </c>
+      <c r="B2097" s="2" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C2097" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2097" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2097" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2097" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2098" s="2">
+        <v>10771</v>
+      </c>
+      <c r="B2098" s="2" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C2098" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2098" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2098" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2098" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2099" s="2">
+        <v>1078</v>
+      </c>
+      <c r="B2099" s="2" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C2099" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2099" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2099" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2099" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2100" s="2">
+        <v>10752</v>
+      </c>
+      <c r="B2100" s="2" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C2100" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2100" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2100" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2100" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2101" s="2">
+        <v>1076</v>
+      </c>
+      <c r="B2101" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C2101" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2101" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2101" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2101" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2102" s="2">
+        <v>1010</v>
+      </c>
+      <c r="B2102" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2102" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2102" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2102" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2102" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2103" s="2">
+        <v>1017</v>
+      </c>
+      <c r="B2103" s="2" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C2103" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2103" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2103" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2103" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2104" s="2">
+        <v>1015</v>
+      </c>
+      <c r="B2104" s="2" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C2104" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2104" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2104" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2104" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2105" s="2">
+        <v>1187</v>
+      </c>
+      <c r="B2105" s="2" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C2105" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2105" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2105" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2105" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2106" s="2">
+        <v>1201</v>
+      </c>
+      <c r="B2106" s="2" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C2106" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2106" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2106" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2106" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2107" s="2">
+        <v>1205</v>
+      </c>
+      <c r="B2107" s="2" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C2107" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2107" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2107" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2107" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2108" s="2">
+        <v>11021</v>
+      </c>
+      <c r="B2108" s="2" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C2108" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2108" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2108" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2108" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2109" s="2">
+        <v>1102</v>
+      </c>
+      <c r="B2109" s="2" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C2109" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2109" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2109" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2109" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2110" s="2">
+        <v>11022</v>
+      </c>
+      <c r="B2110" s="2" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C2110" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2110" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2110" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2110" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2111" s="2">
+        <v>11023</v>
+      </c>
+      <c r="B2111" s="2" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C2111" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2111" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2111" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2111" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2112" s="2">
+        <v>11024</v>
+      </c>
+      <c r="B2112" s="2" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C2112" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2112" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2112" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2112" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2113" s="2">
+        <v>1099</v>
+      </c>
+      <c r="B2113" s="2" t="s">
+        <v>2120</v>
+      </c>
+      <c r="C2113" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2113" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2113" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2113" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2114" s="2">
+        <v>11151</v>
+      </c>
+      <c r="B2114" s="2" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C2114" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2114" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2114" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2114" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2115" s="2">
+        <v>11153</v>
+      </c>
+      <c r="B2115" s="2" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C2115" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2115" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2115" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2115" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2116" s="2">
+        <v>11152</v>
+      </c>
+      <c r="B2116" s="2" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C2116" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2116" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2116" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2116" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2117" s="2">
+        <v>11162</v>
+      </c>
+      <c r="B2117" s="2" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C2117" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2117" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2117" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2117" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2118" s="2">
+        <v>11163</v>
+      </c>
+      <c r="B2118" s="2" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C2118" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2118" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2118" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2118" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2119" s="2">
+        <v>11161</v>
+      </c>
+      <c r="B2119" s="2" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C2119" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2119" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2119" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2119" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2120" s="2">
+        <v>1168</v>
+      </c>
+      <c r="B2120" s="2" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C2120" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2120" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2120" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2120" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2121" s="2">
+        <v>1183</v>
+      </c>
+      <c r="B2121" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C2121" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2121" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2121" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2121" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2122" s="2">
+        <v>11221</v>
+      </c>
+      <c r="B2122" s="2" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C2122" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2122" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2122" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2122" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2123" s="2">
+        <v>1122</v>
+      </c>
+      <c r="B2123" s="2" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C2123" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2123" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2123" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2123" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2124" s="2">
+        <v>11222</v>
+      </c>
+      <c r="B2124" s="2" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C2124" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2124" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2124" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2124" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2125" s="2">
+        <v>11212</v>
+      </c>
+      <c r="B2125" s="2" t="s">
+        <v>2169</v>
+      </c>
+      <c r="C2125" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2125" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2125" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2125" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2126" s="2">
+        <v>1121</v>
+      </c>
+      <c r="B2126" s="2" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C2126" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2126" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2126" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2126" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2127" s="2">
+        <v>11211</v>
+      </c>
+      <c r="B2127" s="2" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C2127" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2127" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2127" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2127" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2128" s="2">
+        <v>11201</v>
+      </c>
+      <c r="B2128" s="2" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C2128" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2128" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2128" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2128" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2129" s="2">
+        <v>11202</v>
+      </c>
+      <c r="B2129" s="2" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C2129" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2129" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2129" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F2129" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2130" s="2">
+        <v>10941</v>
+      </c>
+      <c r="B2130" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2130" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2130" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2130" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2130" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2131" s="2">
+        <v>10952</v>
+      </c>
+      <c r="B2131" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2131" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2131" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2131" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2131" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2132" s="2">
+        <v>10951</v>
+      </c>
+      <c r="B2132" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2132" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2132" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2132" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2132" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2133" s="2">
+        <v>1095</v>
+      </c>
+      <c r="B2133" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2133" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2133" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2133" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2133" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2134" s="2">
+        <v>10931</v>
+      </c>
+      <c r="B2134" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2134" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2134" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2134" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2134" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2135" s="2">
+        <v>1093</v>
+      </c>
+      <c r="B2135" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2135" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2135" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2135" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2135" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2136" s="2">
+        <v>10932</v>
+      </c>
+      <c r="B2136" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2136" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2136" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2136" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2136" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2137" s="2">
+        <v>10952</v>
+      </c>
+      <c r="B2137" s="2" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C2137" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2137" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2137" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2137" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2138" s="2">
+        <v>10951</v>
+      </c>
+      <c r="B2138" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2138" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2138" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2138" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2138" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2139" s="2">
+        <v>1095</v>
+      </c>
+      <c r="B2139" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2139" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2139" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2139" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2139" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2140" s="2">
+        <v>10931</v>
+      </c>
+      <c r="B2140" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2140" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2140" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2140" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2140" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2141" s="2">
+        <v>1093</v>
+      </c>
+      <c r="B2141" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2141" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2141" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2141" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2141" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2142" s="2">
+        <v>10932</v>
+      </c>
+      <c r="B2142" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2142" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2142" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2142" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2142" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2143" s="2">
+        <v>10941</v>
+      </c>
+      <c r="B2143" s="2" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C2143" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2143" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2143" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2143" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2144" s="2">
+        <v>11071</v>
+      </c>
+      <c r="B2144" s="2" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C2144" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2144" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2144" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2144" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2145" s="2">
+        <v>11072</v>
+      </c>
+      <c r="B2145" s="2" t="s">
+        <v>2108</v>
+      </c>
+      <c r="C2145" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2145" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2145" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2145" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2146" s="2">
+        <v>11091</v>
+      </c>
+      <c r="B2146" s="2" t="s">
+        <v>2109</v>
+      </c>
+      <c r="C2146" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2146" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2146" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2146" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2147" s="2">
+        <v>1107</v>
+      </c>
+      <c r="B2147" s="2" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C2147" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2147" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2147" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2147" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2148" s="2">
+        <v>5963</v>
+      </c>
+      <c r="B2148" s="2" t="s">
+        <v>2146</v>
+      </c>
+      <c r="C2148" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2148" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2148" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2148" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2149" s="2">
+        <v>5859</v>
+      </c>
+      <c r="B2149" s="2" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C2149" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2149" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2149" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2149" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2150" s="2">
+        <v>1175</v>
+      </c>
+      <c r="B2150" s="2" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C2150" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2150" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2150" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2150" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2151" s="2">
+        <v>11841</v>
+      </c>
+      <c r="B2151" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2151" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2151" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2151" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2151" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2152" s="2">
+        <v>11842</v>
+      </c>
+      <c r="B2152" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2152" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2152" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2152" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2152" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2153" s="2">
+        <v>10961</v>
+      </c>
+      <c r="B2153" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2153" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2153" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2153" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2153" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2154" s="2">
+        <v>10971</v>
+      </c>
+      <c r="B2154" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2154" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2154" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2154" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2154" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2155" s="2">
+        <v>10972</v>
+      </c>
+      <c r="B2155" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2155" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2155" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2155" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2155" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2156" s="2">
+        <v>10973</v>
+      </c>
+      <c r="B2156" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2156" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2156" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2156" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2156" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2157" s="2">
+        <v>10981</v>
+      </c>
+      <c r="B2157" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2157" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2157" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2157" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2157" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2158" s="2">
+        <v>1098</v>
+      </c>
+      <c r="B2158" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2158" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2158" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2158" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2158" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2159" s="2">
+        <v>10983</v>
+      </c>
+      <c r="B2159" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2159" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2159" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2159" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2159" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2160" s="2">
+        <v>10982</v>
+      </c>
+      <c r="B2160" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2160" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2160" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2160" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2160" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2161" s="2">
+        <v>10962</v>
+      </c>
+      <c r="B2161" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2161" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2161" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2161" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2161" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2162" s="2">
+        <v>10963</v>
+      </c>
+      <c r="B2162" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2162" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2162" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2162" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2162" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2163" s="2">
+        <v>11691</v>
+      </c>
+      <c r="B2163" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2163" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2163" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2163" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2163" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2164" s="2">
+        <v>11692</v>
+      </c>
+      <c r="B2164" s="2" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C2164" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2164" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2164" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2164" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2165" s="2">
+        <v>10961</v>
+      </c>
+      <c r="B2165" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2165" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2165" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2165" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2165" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2166" s="2">
+        <v>10971</v>
+      </c>
+      <c r="B2166" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2166" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2166" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2166" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2166" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2167" s="2">
+        <v>10972</v>
+      </c>
+      <c r="B2167" s="2" t="s">
+        <v>2091</v>
+      </c>
+      <c r="C2167" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2167" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2167" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2167" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2168" s="2">
+        <v>10973</v>
+      </c>
+      <c r="B2168" s="2" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C2168" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2168" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2168" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2168" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2169" s="2">
+        <v>10981</v>
+      </c>
+      <c r="B2169" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2169" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2169" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2169" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2169" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2170" s="2">
+        <v>1098</v>
+      </c>
+      <c r="B2170" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2170" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2170" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2170" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2170" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2171" s="2">
+        <v>10983</v>
+      </c>
+      <c r="B2171" s="2" t="s">
+        <v>2093</v>
+      </c>
+      <c r="C2171" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2171" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2171" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2171" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2172" s="2">
+        <v>10982</v>
+      </c>
+      <c r="B2172" s="2" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C2172" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2172" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2172" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2172" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2173" s="2">
+        <v>10962</v>
+      </c>
+      <c r="B2173" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2173" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2173" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2173" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2173" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2174" s="2">
+        <v>10963</v>
+      </c>
+      <c r="B2174" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2174" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2174" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2174" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2174" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2175" s="2">
+        <v>11691</v>
+      </c>
+      <c r="B2175" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2175" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2175" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2175" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2175" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2176" s="2">
+        <v>11841</v>
+      </c>
+      <c r="B2176" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2176" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2176" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2176" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2176" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2177" s="2">
+        <v>11692</v>
+      </c>
+      <c r="B2177" s="2" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C2177" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2177" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2177" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2177" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2178" s="2">
+        <v>11842</v>
+      </c>
+      <c r="B2178" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2178" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2178" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2178" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2178" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2179" s="2">
+        <v>4797</v>
+      </c>
+      <c r="B2179" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C2179" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2179" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2179" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2179" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2180" s="2">
+        <v>11131</v>
+      </c>
+      <c r="B2180" s="2" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C2180" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2180" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2180" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2180" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2181" s="2">
+        <v>11132</v>
+      </c>
+      <c r="B2181" s="2" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C2181" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2181" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2181" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2181" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2182" s="2">
+        <v>11133</v>
+      </c>
+      <c r="B2182" s="2" t="s">
+        <v>2114</v>
+      </c>
+      <c r="C2182" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2182" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2182" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2182" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2183" s="2">
+        <v>11102</v>
+      </c>
+      <c r="B2183" s="2" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C2183" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2183" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2183" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2183" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2184" s="2">
+        <v>11103</v>
+      </c>
+      <c r="B2184" s="2" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C2184" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2184" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2184" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2184" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2185" s="2">
+        <v>11121</v>
+      </c>
+      <c r="B2185" s="2" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C2185" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2185" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2185" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2185" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2186" s="2">
+        <v>11122</v>
+      </c>
+      <c r="B2186" s="2" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C2186" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2186" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2186" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2186" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2187" s="2">
+        <v>11123</v>
+      </c>
+      <c r="B2187" s="2" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C2187" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2187" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2187" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2187" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2188" s="2">
+        <v>11101</v>
+      </c>
+      <c r="B2188" s="2" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C2188" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2188" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2188" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2188" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2189" s="2">
+        <v>5961</v>
+      </c>
+      <c r="B2189" s="2" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C2189" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2189" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2189" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2189" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2190" s="2">
+        <v>5860</v>
+      </c>
+      <c r="B2190" s="2" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C2190" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2190" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2190" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2190" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2191" s="2">
+        <v>5861</v>
+      </c>
+      <c r="B2191" s="2" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C2191" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2191" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2191" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2191" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2192" s="2">
+        <v>5863</v>
+      </c>
+      <c r="B2192" s="2" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2192" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2192" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2192" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2192" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2193" s="2">
+        <v>1174</v>
+      </c>
+      <c r="B2193" s="2" t="s">
+        <v>2159</v>
+      </c>
+      <c r="C2193" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2193" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2193" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2193" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2194" s="2">
+        <v>1186</v>
+      </c>
+      <c r="B2194" s="2" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C2194" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2194" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2194" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2194" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2195" s="2">
+        <v>11272</v>
+      </c>
+      <c r="B2195" s="2" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C2195" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2195" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2195" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2195" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2196" s="2">
+        <v>11271</v>
+      </c>
+      <c r="B2196" s="2" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C2196" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2196" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2196" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2196" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2197" s="2">
+        <v>12041</v>
+      </c>
+      <c r="B2197" s="2" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C2197" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2197" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2197" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2197" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2198" s="2">
+        <v>12042</v>
+      </c>
+      <c r="B2198" s="2" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C2198" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2198" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2198" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2198" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2199" s="2">
+        <v>12043</v>
+      </c>
+      <c r="B2199" s="2" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C2199" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2199" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2199" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2199" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2200" s="2">
+        <v>5650</v>
+      </c>
+      <c r="B2200" s="2" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C2200" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2200" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2200" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2200" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2201" s="2">
+        <v>1173</v>
+      </c>
+      <c r="B2201" s="2" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2201" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2201" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2201" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F2201" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2202" s="2">
+        <v>11011</v>
+      </c>
+      <c r="B2202" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2202" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2202" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2202" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2202" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2203" s="2">
+        <v>11003</v>
+      </c>
+      <c r="B2203" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2203" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2203" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2203" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2203" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2204" s="2">
+        <v>11002</v>
+      </c>
+      <c r="B2204" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2204" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2204" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2204" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2204" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2205" s="2">
+        <v>11001</v>
+      </c>
+      <c r="B2205" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2205" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2205" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2205" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2205" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2206" s="2">
+        <v>11011</v>
+      </c>
+      <c r="B2206" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2206" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2206" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2206" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2206" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2207" s="2">
+        <v>11003</v>
+      </c>
+      <c r="B2207" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2207" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2207" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2207" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2207" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2208" s="2">
+        <v>11002</v>
+      </c>
+      <c r="B2208" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C2208" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2208" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2208" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2208" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2209" s="2">
+        <v>11001</v>
+      </c>
+      <c r="B2209" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2209" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2209" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2209" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2209" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2210" s="2">
+        <v>1105</v>
+      </c>
+      <c r="B2210" s="2" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C2210" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2210" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2210" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2210" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2211" s="2">
+        <v>1106</v>
+      </c>
+      <c r="B2211" s="2" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C2211" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2211" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2211" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2211" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2212" s="2">
+        <v>1103</v>
+      </c>
+      <c r="B2212" s="2" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C2212" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2212" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2212" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2212" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2213" s="2">
+        <v>1104</v>
+      </c>
+      <c r="B2213" s="2" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C2213" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2213" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2213" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2213" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2214" s="2">
+        <v>11081</v>
+      </c>
+      <c r="B2214" s="2" t="s">
+        <v>2125</v>
+      </c>
+      <c r="C2214" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2214" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2214" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2214" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2215" s="2">
+        <v>5862</v>
+      </c>
+      <c r="B2215" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C2215" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2215" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2215" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2215" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2216" s="2">
+        <v>5899</v>
+      </c>
+      <c r="B2216" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C2216" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2216" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2216" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F2216" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2217" s="2">
+        <v>10891</v>
+      </c>
+      <c r="B2217" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2217" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2217" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2217" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2217" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2218" s="2">
+        <v>1089</v>
+      </c>
+      <c r="B2218" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2218" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2218" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2218" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2218" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2219" s="2">
+        <v>10892</v>
+      </c>
+      <c r="B2219" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2219" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2219" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2219" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2219" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2220" s="2">
+        <v>1090</v>
+      </c>
+      <c r="B2220" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2220" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2220" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2220" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2220" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2221" s="2">
+        <v>10912</v>
+      </c>
+      <c r="B2221" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2221" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2221" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2221" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2221" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2222" s="2">
+        <v>1092</v>
+      </c>
+      <c r="B2222" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2222" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2222" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2222" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2222" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2223" s="2">
+        <v>10911</v>
+      </c>
+      <c r="B2223" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2223" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2223" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2223" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2223" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2224" s="2">
+        <v>1091</v>
+      </c>
+      <c r="B2224" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2224" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2224" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2224" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2224" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2225" s="2">
+        <v>10802</v>
+      </c>
+      <c r="B2225" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2225" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2225" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2225" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2225" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2226" s="2">
+        <v>10822</v>
+      </c>
+      <c r="B2226" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2226" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2226" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2226" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2226" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2227" s="2">
+        <v>1083</v>
+      </c>
+      <c r="B2227" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2227" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2227" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2227" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2227" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2228" s="2">
+        <v>1081</v>
+      </c>
+      <c r="B2228" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2228" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2228" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2228" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2228" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2229" s="2">
+        <v>10821</v>
+      </c>
+      <c r="B2229" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2229" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2229" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2229" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2229" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2230" s="2">
+        <v>10801</v>
+      </c>
+      <c r="B2230" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2230" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2230" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2230" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2230" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2231" s="2">
+        <v>1080</v>
+      </c>
+      <c r="B2231" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2231" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2231" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2231" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2231" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2232" s="2">
+        <v>1084</v>
+      </c>
+      <c r="B2232" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2232" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2232" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2232" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2232" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2233" s="2">
+        <v>1086</v>
+      </c>
+      <c r="B2233" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2233" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2233" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2233" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2233" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2234" s="2">
+        <v>10851</v>
+      </c>
+      <c r="B2234" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2234" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2234" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2234" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2234" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2235" s="2">
+        <v>1085</v>
+      </c>
+      <c r="B2235" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2235" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2235" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2235" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2235" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2236" s="2">
+        <v>10852</v>
+      </c>
+      <c r="B2236" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2236" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2236" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2236" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2236" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2237" s="2">
+        <v>10871</v>
+      </c>
+      <c r="B2237" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2237" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2237" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2237" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2237" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2238" s="2">
+        <v>1087</v>
+      </c>
+      <c r="B2238" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2238" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2238" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2238" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2238" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2239" s="2">
+        <v>10872</v>
+      </c>
+      <c r="B2239" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2239" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2239" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2239" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2239" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2240" s="2">
+        <v>1088</v>
+      </c>
+      <c r="B2240" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2240" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2240" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2240" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2240" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2241" s="2">
+        <v>1082</v>
+      </c>
+      <c r="B2241" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2241" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2241" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2241" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2241" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2242" s="2">
+        <v>10802</v>
+      </c>
+      <c r="B2242" s="2" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C2242" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2242" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2242" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2242" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2243" s="2">
+        <v>10822</v>
+      </c>
+      <c r="B2243" s="2" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C2243" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2243" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2243" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2243" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2244" s="2">
+        <v>1083</v>
+      </c>
+      <c r="B2244" s="2" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C2244" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2244" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2244" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2244" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2245" s="2">
+        <v>1081</v>
+      </c>
+      <c r="B2245" s="2" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C2245" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2245" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2245" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2245" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2246" s="2">
+        <v>1082</v>
+      </c>
+      <c r="B2246" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2246" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2246" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2246" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2246" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2247" s="2">
+        <v>10821</v>
+      </c>
+      <c r="B2247" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2247" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2247" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2247" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2247" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2248" s="2">
+        <v>1080</v>
+      </c>
+      <c r="B2248" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2248" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2248" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2248" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2248" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2249" s="2">
+        <v>10801</v>
+      </c>
+      <c r="B2249" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2249" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2249" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2249" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2249" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2250" s="2">
+        <v>1084</v>
+      </c>
+      <c r="B2250" s="2" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C2250" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2250" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2250" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2250" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2251" s="2">
+        <v>1086</v>
+      </c>
+      <c r="B2251" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2251" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2251" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2251" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2251" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2252" s="2">
+        <v>1085</v>
+      </c>
+      <c r="B2252" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2252" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2252" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2252" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2252" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2253" s="2">
+        <v>10851</v>
+      </c>
+      <c r="B2253" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2253" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2253" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2253" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2253" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2254" s="2">
+        <v>10852</v>
+      </c>
+      <c r="B2254" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2254" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2254" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2254" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2254" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2255" s="2">
+        <v>1087</v>
+      </c>
+      <c r="B2255" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2255" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2255" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2255" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2255" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2256" s="2">
+        <v>10871</v>
+      </c>
+      <c r="B2256" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2256" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2256" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2256" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2256" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2257" s="2">
+        <v>10872</v>
+      </c>
+      <c r="B2257" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2257" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2257" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2257" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2257" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2258" s="2">
+        <v>1088</v>
+      </c>
+      <c r="B2258" s="2" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C2258" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2258" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2258" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2258" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2259" s="2">
+        <v>1089</v>
+      </c>
+      <c r="B2259" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2259" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2259" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2259" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2259" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2260" s="2">
+        <v>10891</v>
+      </c>
+      <c r="B2260" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2260" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2260" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2260" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2260" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2261" s="2">
+        <v>10892</v>
+      </c>
+      <c r="B2261" s="2" t="s">
+        <v>2085</v>
+      </c>
+      <c r="C2261" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2261" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2261" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2261" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2262" s="2">
+        <v>1090</v>
+      </c>
+      <c r="B2262" s="2" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C2262" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2262" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2262" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2262" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2263" s="2">
+        <v>10912</v>
+      </c>
+      <c r="B2263" s="2" t="s">
+        <v>2087</v>
+      </c>
+      <c r="C2263" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2263" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2263" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2263" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2264" s="2">
+        <v>1092</v>
+      </c>
+      <c r="B2264" s="2" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C2264" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2264" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2264" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2264" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2265" s="2">
+        <v>1091</v>
+      </c>
+      <c r="B2265" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2265" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2265" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2265" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2265" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2266" s="2">
+        <v>10911</v>
+      </c>
+      <c r="B2266" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2266" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2266" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2266" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2266" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2267" s="2">
+        <v>5975</v>
+      </c>
+      <c r="B2267" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C2267" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2267" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2267" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2267" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2268" s="2">
+        <v>5962</v>
+      </c>
+      <c r="B2268" s="2" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C2268" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2268" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2268" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2268" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2269" s="2">
+        <v>1196</v>
+      </c>
+      <c r="B2269" s="2" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C2269" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2269" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2269" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2269" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2270" s="2">
+        <v>5874</v>
+      </c>
+      <c r="B2270" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C2270" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2270" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2270" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2270" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2271" s="2">
+        <v>1170</v>
+      </c>
+      <c r="B2271" s="2" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C2271" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2271" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2271" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2271" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2272" s="2">
+        <v>1199</v>
+      </c>
+      <c r="B2272" s="2" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C2272" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2272" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2272" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2272" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2273" s="2">
+        <v>6000</v>
+      </c>
+      <c r="B2273" s="2" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C2273" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2273" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2273" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2273" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2274" s="2">
+        <v>11192</v>
+      </c>
+      <c r="B2274" s="2" t="s">
+        <v>2174</v>
+      </c>
+      <c r="C2274" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2274" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2274" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2274" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2275" s="2">
+        <v>11931</v>
+      </c>
+      <c r="B2275" s="2" t="s">
+        <v>2175</v>
+      </c>
+      <c r="C2275" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2275" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2275" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2275" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2276" s="2">
+        <v>11932</v>
+      </c>
+      <c r="B2276" s="2" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C2276" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2276" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2276" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2276" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2277" s="2">
+        <v>11171</v>
+      </c>
+      <c r="B2277" s="2" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C2277" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2277" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2277" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2277" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2278" s="2">
+        <v>11172</v>
+      </c>
+      <c r="B2278" s="2" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C2278" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2278" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2278" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2278" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2279" s="2">
+        <v>11191</v>
+      </c>
+      <c r="B2279" s="2" t="s">
+        <v>2179</v>
+      </c>
+      <c r="C2279" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2279" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2279" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2279" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2280" s="2">
+        <v>11911</v>
+      </c>
+      <c r="B2280" s="2" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C2280" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2280" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2280" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2280" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2281" s="2">
+        <v>11912</v>
+      </c>
+      <c r="B2281" s="2" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C2281" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2281" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2281" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2281" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2282" s="2">
+        <v>11181</v>
+      </c>
+      <c r="B2282" s="2" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C2282" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2282" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2282" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2282" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2283" s="2">
+        <v>1118</v>
+      </c>
+      <c r="B2283" s="2" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C2283" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2283" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2283" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2283" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2284" s="2">
+        <v>11182</v>
+      </c>
+      <c r="B2284" s="2" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C2284" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2284" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2284" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2284" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2285" s="2">
+        <v>11801</v>
+      </c>
+      <c r="B2285" s="2" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C2285" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2285" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2285" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2285" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2286" s="2">
+        <v>11802</v>
+      </c>
+      <c r="B2286" s="2" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C2286" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2286" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E2286" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2286" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2287" s="2">
+        <v>1182</v>
+      </c>
+      <c r="B2287" s="2" t="s">
+        <v>2236</v>
+      </c>
+      <c r="C2287" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2287" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2287" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2287" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2288" s="2">
+        <v>11111</v>
+      </c>
+      <c r="B2288" s="2" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C2288" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2288" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2288" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2288" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2289" s="2">
+        <v>1111</v>
+      </c>
+      <c r="B2289" s="2" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C2289" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2289" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2289" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2289" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2290" s="2">
+        <v>11112</v>
+      </c>
+      <c r="B2290" s="2" t="s">
+        <v>2111</v>
+      </c>
+      <c r="C2290" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2290" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2290" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F2290" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2291" s="2">
+        <v>11141</v>
+      </c>
+      <c r="B2291" s="2" t="s">
         <v>2057</v>
       </c>
-      <c r="C2089" s="1" t="s">
+      <c r="C2291" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D2089" s="2" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E2089" t="s">
-        <v>1655</v>
-      </c>
-      <c r="F2089" s="1" t="s">
-        <v>2058</v>
-      </c>
-    </row>
-    <row r="2090" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2090" s="1">
-        <v>1102</v>
-      </c>
-      <c r="B2090" s="1" t="s">
-        <v>2059</v>
-      </c>
-      <c r="C2090" s="1" t="s">
+      <c r="D2291" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2291" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2291" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2292" s="2">
+        <v>5872</v>
+      </c>
+      <c r="B2292" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C2292" s="2" t="s">
         <v>2049</v>
       </c>
-      <c r="D2090" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E2090" t="s">
+      <c r="D2292" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2292" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F2292" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2293" s="2">
+        <v>5870</v>
+      </c>
+      <c r="B2293" s="2" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C2293" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2293" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2293" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F2293" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2294" s="2">
+        <v>5871</v>
+      </c>
+      <c r="B2294" s="2" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C2294" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2294" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2294" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F2294" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2295" s="2">
+        <v>5873</v>
+      </c>
+      <c r="B2295" s="2" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C2295" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2295" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2295" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F2295" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2296" s="2">
+        <v>5858</v>
+      </c>
+      <c r="B2296" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C2296" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2296" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2296" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F2296" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2297" s="2">
+        <v>1197</v>
+      </c>
+      <c r="B2297" s="2" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C2297" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2297" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2297" s="4" t="s">
         <v>1656</v>
       </c>
-      <c r="F2090" s="1" t="s">
-        <v>2058</v>
+      <c r="F2297" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2298" s="2">
+        <v>1206</v>
+      </c>
+      <c r="B2298" s="2" t="s">
+        <v>2157</v>
+      </c>
+      <c r="C2298" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2298" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2298" s="4" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2298" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2299" s="2">
+        <v>1128</v>
+      </c>
+      <c r="B2299" s="2" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C2299" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2299" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2299" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2299" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2300" s="2">
+        <v>1209</v>
+      </c>
+      <c r="B2300" s="2" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C2300" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2300" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2300" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2300" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2301" s="2">
+        <v>1165</v>
+      </c>
+      <c r="B2301" s="2" t="s">
+        <v>2188</v>
+      </c>
+      <c r="C2301" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2301" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2301" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2301" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2302" s="2">
+        <v>1164</v>
+      </c>
+      <c r="B2302" s="2" t="s">
+        <v>2189</v>
+      </c>
+      <c r="C2302" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2302" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2302" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2302" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2303" s="2">
+        <v>1163</v>
+      </c>
+      <c r="B2303" s="2" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C2303" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2303" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2303" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2303" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2304" s="2">
+        <v>1162</v>
+      </c>
+      <c r="B2304" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="C2304" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2304" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2304" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2304" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2305" s="2">
+        <v>1161</v>
+      </c>
+      <c r="B2305" s="2" t="s">
+        <v>2192</v>
+      </c>
+      <c r="C2305" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2305" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2305" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2305" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2306" s="2">
+        <v>1160</v>
+      </c>
+      <c r="B2306" s="2" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C2306" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2306" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2306" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2306" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2307" s="2">
+        <v>1150</v>
+      </c>
+      <c r="B2307" s="2" t="s">
+        <v>2194</v>
+      </c>
+      <c r="C2307" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2307" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2307" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2307" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2308" s="2">
+        <v>1157</v>
+      </c>
+      <c r="B2308" s="2" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C2308" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2308" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2308" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2308" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2309" s="2">
+        <v>1151</v>
+      </c>
+      <c r="B2309" s="2" t="s">
+        <v>2196</v>
+      </c>
+      <c r="C2309" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2309" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2309" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2309" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2310" s="2">
+        <v>1152</v>
+      </c>
+      <c r="B2310" s="2" t="s">
+        <v>2197</v>
+      </c>
+      <c r="C2310" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2310" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2310" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2310" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2311" s="2">
+        <v>1153</v>
+      </c>
+      <c r="B2311" s="2" t="s">
+        <v>2198</v>
+      </c>
+      <c r="C2311" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2311" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2311" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2311" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2312" s="2">
+        <v>1154</v>
+      </c>
+      <c r="B2312" s="2" t="s">
+        <v>2199</v>
+      </c>
+      <c r="C2312" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2312" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2312" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2312" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2313" s="2">
+        <v>1155</v>
+      </c>
+      <c r="B2313" s="2" t="s">
+        <v>2200</v>
+      </c>
+      <c r="C2313" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2313" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2313" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2313" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2314" s="2">
+        <v>1156</v>
+      </c>
+      <c r="B2314" s="2" t="s">
+        <v>2201</v>
+      </c>
+      <c r="C2314" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2314" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2314" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2314" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2315" s="2">
+        <v>1207</v>
+      </c>
+      <c r="B2315" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C2315" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2315" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2315" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2315" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2316" s="2">
+        <v>1158</v>
+      </c>
+      <c r="B2316" s="2" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C2316" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2316" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2316" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2316" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2317" s="2">
+        <v>1159</v>
+      </c>
+      <c r="B2317" s="2" t="s">
+        <v>2204</v>
+      </c>
+      <c r="C2317" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2317" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2317" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2317" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2318" s="2">
+        <v>1139</v>
+      </c>
+      <c r="B2318" s="2" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C2318" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2318" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2318" s="4" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2318" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2319" s="2">
+        <v>1140</v>
+      </c>
+      <c r="B2319" s="2" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C2319" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2319" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2319" s="4" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2319" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2320" s="2">
+        <v>1141</v>
+      </c>
+      <c r="B2320" s="2" t="s">
+        <v>2207</v>
+      </c>
+      <c r="C2320" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2320" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2320" s="4" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2320" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2321" s="2">
+        <v>1142</v>
+      </c>
+      <c r="B2321" s="2" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C2321" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2321" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2321" s="4" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2321" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2322" s="2">
+        <v>1143</v>
+      </c>
+      <c r="B2322" s="2" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C2322" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2322" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2322" s="4" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2322" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2323" s="2">
+        <v>1144</v>
+      </c>
+      <c r="B2323" s="2" t="s">
+        <v>2210</v>
+      </c>
+      <c r="C2323" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2323" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2323" s="4" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2323" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2324" s="2">
+        <v>1145</v>
+      </c>
+      <c r="B2324" s="2" t="s">
+        <v>2211</v>
+      </c>
+      <c r="C2324" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2324" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2324" s="4" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2324" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2325" s="2">
+        <v>1146</v>
+      </c>
+      <c r="B2325" s="2" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C2325" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2325" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2325" s="4" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2325" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2326" s="2">
+        <v>1147</v>
+      </c>
+      <c r="B2326" s="2" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C2326" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2326" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2326" s="4" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2326" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2327" s="2">
+        <v>1148</v>
+      </c>
+      <c r="B2327" s="2" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C2327" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2327" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2327" s="4" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2327" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2328" s="2">
+        <v>1149</v>
+      </c>
+      <c r="B2328" s="2" t="s">
+        <v>2215</v>
+      </c>
+      <c r="C2328" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2328" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2328" s="4" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2328" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2329" s="2">
+        <v>1129</v>
+      </c>
+      <c r="B2329" s="2" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C2329" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2329" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2329" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2329" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2330" s="2">
+        <v>1130</v>
+      </c>
+      <c r="B2330" s="2" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C2330" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2330" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2330" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2330" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2331" s="2">
+        <v>1131</v>
+      </c>
+      <c r="B2331" s="2" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C2331" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2331" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2331" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2331" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2332" s="2">
+        <v>1132</v>
+      </c>
+      <c r="B2332" s="2" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2332" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2332" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2332" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2332" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2333" s="2">
+        <v>1133</v>
+      </c>
+      <c r="B2333" s="2" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C2333" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2333" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2333" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2333" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2334" s="2">
+        <v>1134</v>
+      </c>
+      <c r="B2334" s="2" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C2334" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2334" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2334" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2334" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2335" s="2">
+        <v>1135</v>
+      </c>
+      <c r="B2335" s="2" t="s">
+        <v>2222</v>
+      </c>
+      <c r="C2335" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2335" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2335" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2335" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2336" s="2">
+        <v>1136</v>
+      </c>
+      <c r="B2336" s="2" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C2336" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2336" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2336" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2336" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2337" s="2">
+        <v>1137</v>
+      </c>
+      <c r="B2337" s="2" t="s">
+        <v>2224</v>
+      </c>
+      <c r="C2337" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2337" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2337" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2337" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2338" s="2">
+        <v>1138</v>
+      </c>
+      <c r="B2338" s="2" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C2338" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2338" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E2338" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2338" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2339" s="2">
+        <v>11231</v>
+      </c>
+      <c r="B2339" s="2" t="s">
+        <v>2230</v>
+      </c>
+      <c r="C2339" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2339" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E2339" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2339" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2340" s="2">
+        <v>1124</v>
+      </c>
+      <c r="B2340" s="2" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C2340" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2340" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E2340" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2340" s="2" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2341" s="2">
+        <v>1200</v>
+      </c>
+      <c r="B2341" s="2" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C2341" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D2341" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E2341" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F2341" s="2" t="s">
+        <v>2237</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>